--- a/test_results/claude_sonnet_4_5_thinking/统计表格.xlsx
+++ b/test_results/claude_sonnet_4_5_thinking/统计表格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\111\新建文件夹\数据分析\分析结果\claude_sonnet_4_5_thinking\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\111\LLM-NeedleInAHaystack\test_results\claude_sonnet_4_5_thinking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AFD4C5-0966-44F6-9CD7-412825725C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCA2EFC-3C4E-46F6-A199-95C02C6C693A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{58898F7C-67C2-4EC0-A511-F699C1A6044A}"/>
+    <workbookView xWindow="2220" yWindow="710" windowWidth="21200" windowHeight="13630" xr2:uid="{58898F7C-67C2-4EC0-A511-F699C1A6044A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -191,6 +191,9 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-BA3C-4E2F-AF9B-AAABE190EF06}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:spPr>
@@ -293,31 +296,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>91.88</c:v>
+                  <c:v>96.46</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>85.45</c:v>
+                  <c:v>91.09</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>87.56</c:v>
+                  <c:v>90.32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>95</c:v>
+                  <c:v>97.7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>91.48</c:v>
+                  <c:v>96.79</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>86.11</c:v>
+                  <c:v>92.27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>85.98</c:v>
+                  <c:v>91.36</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>72.98</c:v>
+                  <c:v>85.36</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>54.19</c:v>
+                  <c:v>75.430000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1277,6 +1280,9 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-2BBD-4C26-B010-F627C86F5C7E}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:spPr>
@@ -1382,34 +1388,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>91.88</c:v>
+                  <c:v>96.46</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>85.45</c:v>
+                  <c:v>91.09</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>87.56</c:v>
+                  <c:v>90.32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>95</c:v>
+                  <c:v>97.7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>91.48</c:v>
+                  <c:v>96.79</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>86.11</c:v>
+                  <c:v>92.27</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>85.98</c:v>
+                  <c:v>91.36</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>72.98</c:v>
+                  <c:v>85.36</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>54.19</c:v>
+                  <c:v>75.430000000000007</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38.21</c:v>
+                  <c:v>66.87</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3942,34 +3948,34 @@
         <v>2</v>
       </c>
       <c r="B8">
-        <v>91.88</v>
+        <v>96.46</v>
       </c>
       <c r="C8">
-        <v>85.45</v>
+        <v>91.09</v>
       </c>
       <c r="D8">
-        <v>87.56</v>
+        <v>90.32</v>
       </c>
       <c r="E8">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="F8">
-        <v>91.48</v>
+        <v>96.79</v>
       </c>
       <c r="G8">
-        <v>86.11</v>
+        <v>92.27</v>
       </c>
       <c r="H8">
-        <v>85.98</v>
+        <v>91.36</v>
       </c>
       <c r="I8">
-        <v>72.98</v>
+        <v>85.36</v>
       </c>
       <c r="J8">
-        <v>54.19</v>
+        <v>75.430000000000007</v>
       </c>
       <c r="K8">
-        <v>38.21</v>
+        <v>66.87</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
